--- a/current-excel-manifests/AssaySpatialTranscriptomicsMetadataTemplate.xlsx
+++ b/current-excel-manifests/AssaySpatialTranscriptomicsMetadataTemplate.xlsx
@@ -252,7 +252,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="148">
   <si>
     <t>Component</t>
   </si>
@@ -566,6 +566,9 @@
     <t>nirs</t>
   </si>
   <si>
+    <t>parquet</t>
+  </si>
+  <si>
     <t>pdf</t>
   </si>
   <si>
@@ -681,6 +684,9 @@
   </si>
   <si>
     <t>wiggle</t>
+  </si>
+  <si>
+    <t>xenium</t>
   </si>
   <si>
     <t>xml</t>
@@ -49136,11 +49142,11 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="D2:D1000">
-      <formula1>Sheet2!$D$2:$D$97</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="E2:E1000">
       <formula1>Sheet2!$E$2:$E$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="D2:D1000">
+      <formula1>Sheet2!$D$2:$D$99</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId2"/>
@@ -49784,6 +49790,16 @@
         <v>145</v>
       </c>
     </row>
+    <row r="98">
+      <c r="D98" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="D99" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
